--- a/target/test-classes/TestData.xlsx
+++ b/target/test-classes/TestData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\eclipse-workspace\Practice_HRM\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5F5CC5-3CF8-40C4-BF7A-9EB372D736C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4A5FED-6F3B-44D9-8846-1FD9A5C3D49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
     <t>Test</t>
   </si>
   <si>
-    <t>check</t>
+    <t>ADMIN</t>
   </si>
 </sst>
 </file>
